--- a/georgia_ev_intelligence/outputs/child_chunks.xlsx
+++ b/georgia_ev_intelligence/outputs/child_chunks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,6 +459,7 @@
           <t>chunk_type: identity
 company: acm georgia llc
 category: Tier 2/3
+state: Georgia
 industry_group: Textile Products
 updated_location: Warrenton, Warren County</t>
         </is>
@@ -536,6 +537,7 @@
         <is>
           <t>chunk_type: location_employment
 company: acm georgia llc
+state: Georgia
 updated_location: Warrenton, Warren County
 address: 975 Thomson Hwy, Warrenton, GA 30828
 latitude: 33.4122927
@@ -592,6 +594,7 @@
           <t>chunk_type: identity
 company: adient
 category: Tier 2/3
+state: Georgia
 industry_group: Textile Products
 updated_location: West Point, Harris County</t>
         </is>
@@ -669,6 +672,7 @@
         <is>
           <t>chunk_type: location_employment
 company: adient
+state: Georgia
 updated_location: West Point, Harris County
 address: 1700 S Progress Pkwy, West Point, GA 31833
 latitude: 32.8486888
@@ -725,6 +729,7 @@
           <t>chunk_type: identity
 company: advics manufacturing georgia llc
 category: Tier 2/3
+state: Georgia
 industry_group: Textile Products
 updated_location: LaGrange, Troup County</t>
         </is>
@@ -802,6 +807,7 @@
         <is>
           <t>chunk_type: location_employment
 company: advics manufacturing georgia llc
+state: Georgia
 updated_location: LaGrange, Troup County
 address: 1621 Lukken Industrial Dr W, LaGrange, GA 30240
 latitude: 33.0113943
@@ -858,6 +864,7 @@
           <t>chunk_type: identity
 company: ajin georgia
 category: Tier 2/3
+state: Georgia
 industry_group: Textile Products
 updated_location: Register, Bulloch County</t>
         </is>
@@ -935,6 +942,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ajin georgia
+state: Georgia
 updated_location: Register, Bulloch County
 address: 355 Rocky Rd, Register, GA 30452
 latitude: 32.3008535
@@ -991,6 +999,7 @@
           <t>chunk_type: identity
 company: albaform inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Textile Products
 updated_location: Flowery Branch, Hall County</t>
         </is>
@@ -1068,6 +1077,7 @@
         <is>
           <t>chunk_type: location_employment
 company: albaform inc.
+state: Georgia
 updated_location: Flowery Branch, Hall County
 address: 6505 McEver Rd, Flowery Branch, GA 30542
 latitude: 34.1674763
@@ -1124,6 +1134,7 @@
           <t>chunk_type: identity
 company: anovion technologies
 category: Tier 2/3
+state: Georgia
 industry_group: Textile Products
 updated_location: Bainbridge</t>
         </is>
@@ -1201,6 +1212,7 @@
         <is>
           <t>chunk_type: location_employment
 company: anovion technologies
+state: Georgia
 updated_location: Bainbridge
 address: Bainbridge, GA (street address not publicly confirmed)
 latitude: Unknown
@@ -1257,6 +1269,7 @@
           <t>chunk_type: identity
 company: apache mills inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Paper and Allied Products
 updated_location: Calhoun, Hall County</t>
         </is>
@@ -1334,6 +1347,7 @@
         <is>
           <t>chunk_type: location_employment
 company: apache mills inc.
+state: Georgia
 updated_location: Calhoun, Hall County
 address: 3270 Joe Jerkins Blvd SE, Calhoun, GA 30701
 latitude: 34.1674763
@@ -1390,6 +1404,7 @@
           <t>chunk_type: identity
 company: archer aviation inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Chemicals and Allied Products
 updated_location: Covington, Morgan County</t>
         </is>
@@ -1467,6 +1482,7 @@
         <is>
           <t>chunk_type: location_employment
 company: archer aviation inc.
+state: Georgia
 updated_location: Covington, Morgan County
 address: 2151 Centennial Pkwy NE, Covington, GA 30014
 latitude: 33.5928931
@@ -1523,6 +1539,7 @@
           <t>chunk_type: identity
 company: arising industries inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Norcross, Gwinnett County</t>
         </is>
@@ -1600,6 +1617,7 @@
         <is>
           <t>chunk_type: location_employment
 company: arising industries inc.
+state: Georgia
 updated_location: Norcross, Gwinnett County
 address: 6010 Unity Dr, Norcross, GA 30071
 latitude: 33.9151041
@@ -1656,6 +1674,7 @@
           <t>chunk_type: identity
 company: arising industries inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Chemicals and Allied Products
 updated_location: Norcross, Gwinnett County</t>
         </is>
@@ -1733,6 +1752,7 @@
         <is>
           <t>chunk_type: location_employment
 company: arising industries inc.
+state: Georgia
 updated_location: Norcross, Gwinnett County
 address: 6010 Unity Dr, Norcross, GA 30071
 latitude: 33.9151041
@@ -1789,6 +1809,7 @@
           <t>chunk_type: identity
 company: ascend elements
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Covington, Henry County</t>
         </is>
@@ -1866,6 +1887,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ascend elements
+state: Georgia
 updated_location: Covington, Henry County
 address: 1409 Brampton Ave, Covington, GA 30014
 latitude: 33.3390858
@@ -1922,6 +1944,7 @@
           <t>chunk_type: identity
 company: aspen aerogels
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Statesboro</t>
         </is>
@@ -1999,6 +2022,7 @@
         <is>
           <t>chunk_type: location_employment
 company: aspen aerogels
+state: Georgia
 updated_location: Statesboro
 address: Statesboro, GA (planned plant—construction canceled)
 latitude: Unknown
@@ -2055,6 +2079,7 @@
           <t>chunk_type: identity
 company: aurubis
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Augusta, Richmond County</t>
         </is>
@@ -2132,6 +2157,7 @@
         <is>
           <t>chunk_type: location_employment
 company: aurubis
+state: Georgia
 updated_location: Augusta, Richmond County
 address: 439 Valencia Way, Augusta, GA 30906
 latitude: 33.282551
@@ -2188,6 +2214,7 @@
           <t>chunk_type: identity
 company: avs
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Alpharetta, Forsyth County</t>
         </is>
@@ -2265,6 +2292,7 @@
         <is>
           <t>chunk_type: location_employment
 company: avs
+state: Georgia
 updated_location: Alpharetta, Forsyth County
 address: 6110 McFarland Station Dr, Alpharetta, GA 30004
 latitude: 34.134562
@@ -2321,6 +2349,7 @@
           <t>chunk_type: identity
 company: beaver manufacturing co. inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Mansfield, Newton County</t>
         </is>
@@ -2398,6 +2427,7 @@
         <is>
           <t>chunk_type: location_employment
 company: beaver manufacturing co. inc.
+state: Georgia
 updated_location: Mansfield, Newton County
 address: 12 Ed Needham Dr, Mansfield, GA 30055
 latitude: 33.518502
@@ -2454,6 +2484,7 @@
           <t>chunk_type: identity
 company: big tex trailer manufacturing inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Loganville, Gwinnett County</t>
         </is>
@@ -2531,6 +2562,7 @@
         <is>
           <t>chunk_type: location_employment
 company: big tex trailer manufacturing inc.
+state: Georgia
 updated_location: Loganville, Gwinnett County
 address: 3850 Harrison Rd, Loganville, GA 30052
 latitude: 33.849953
@@ -2587,6 +2619,7 @@
           <t>chunk_type: identity
 company: blue bird corp.
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Fort Valley, Peach County</t>
         </is>
@@ -2664,6 +2697,7 @@
         <is>
           <t>chunk_type: location_employment
 company: blue bird corp.
+state: Georgia
 updated_location: Fort Valley, Peach County
 address: 402 Blue Bird Blvd, Fort Valley, GA 31030
 latitude: 32.561892
@@ -2720,6 +2754,7 @@
           <t>chunk_type: identity
 company: blue ridge manufacturing
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Blue Ridge, Union County</t>
         </is>
@@ -2797,6 +2832,7 @@
         <is>
           <t>chunk_type: location_employment
 company: blue ridge manufacturing
+state: Georgia
 updated_location: Blue Ridge, Union County
 address: 87 Tom Boyd Rd, Blue Ridge, GA 30513
 latitude: 34.8963485
@@ -2853,6 +2889,7 @@
           <t>chunk_type: identity
 company: bonnell aluminum
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Newnan, Coweta County</t>
         </is>
@@ -2930,6 +2967,7 @@
         <is>
           <t>chunk_type: location_employment
 company: bonnell aluminum
+state: Georgia
 updated_location: Newnan, Coweta County
 address: 37 LaGrange St, Newnan, GA 30263
 latitude: 33.3719956
@@ -2986,6 +3024,7 @@
           <t>chunk_type: identity
 company: boogook industries
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Macon, Bibb County</t>
         </is>
@@ -3063,6 +3102,7 @@
         <is>
           <t>chunk_type: location_employment
 company: boogook industries
+state: Georgia
 updated_location: Macon, Bibb County
 address: 2600 Weaver Rd Suite 1-11, Macon, GA 31217
 latitude: 32.8141689
@@ -3119,6 +3159,7 @@
           <t>chunk_type: identity
 company: bosal industries georgia
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Lavonia, Franklin County</t>
         </is>
@@ -3196,6 +3237,7 @@
         <is>
           <t>chunk_type: location_employment
 company: bosal industries georgia
+state: Georgia
 updated_location: Lavonia, Franklin County
 address: 1 Bosal Way, Lavonia, GA 30553
 latitude: 34.4385903
@@ -3252,6 +3294,7 @@
           <t>chunk_type: identity
 company: bosch (automotive division)
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Toccoa, Stephens County</t>
         </is>
@@ -3329,6 +3372,7 @@
         <is>
           <t>chunk_type: location_employment
 company: bosch (automotive division)
+state: Georgia
 updated_location: Toccoa, Stephens County
 address: 1241 Meadowbrook Dr, Toccoa, GA 30577
 latitude: 34.5288916
@@ -3385,6 +3429,7 @@
           <t>chunk_type: identity
 company: bridgestone bandag
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Griffin, Spalding County</t>
         </is>
@@ -3462,6 +3507,7 @@
         <is>
           <t>chunk_type: location_employment
 company: bridgestone bandag
+state: Georgia
 updated_location: Griffin, Spalding County
 address: 801 Greenbelt Pkwy, Griffin, GA 30223
 latitude: 33.2369594
@@ -3518,6 +3564,7 @@
           <t>chunk_type: identity
 company: carcoustics usa
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Buford, Gwinnett County</t>
         </is>
@@ -3595,6 +3642,7 @@
         <is>
           <t>chunk_type: location_employment
 company: carcoustics usa
+state: Georgia
 updated_location: Buford, Gwinnett County
 address: 4740 S Lee St, Buford, GA 30518
 latitude: 34.1143595
@@ -3651,6 +3699,7 @@
           <t>chunk_type: identity
 company: club car llc
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Evans, Columbia County</t>
         </is>
@@ -3728,6 +3777,7 @@
         <is>
           <t>chunk_type: location_employment
 company: club car llc
+state: Georgia
 updated_location: Evans, Columbia County
 address: 4125 Washington Rd, Evans, GA 30809
 latitude: 33.5200327
@@ -3784,6 +3834,7 @@
           <t>chunk_type: identity
 company: constellium automotive usa
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Cartersville, Bartow County</t>
         </is>
@@ -3861,6 +3912,7 @@
         <is>
           <t>chunk_type: location_employment
 company: constellium automotive usa
+state: Georgia
 updated_location: Cartersville, Bartow County
 address: 1 Constellium Way, Cartersville, GA 30120
 latitude: 34.1773609
@@ -3917,6 +3969,7 @@
           <t>chunk_type: identity
 company: continental automotive
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Fairburn, Fulton County</t>
         </is>
@@ -3994,6 +4047,7 @@
         <is>
           <t>chunk_type: location_employment
 company: continental automotive
+state: Georgia
 updated_location: Fairburn, Fulton County
 address: 7310 Oakley Industrial Blvd, Fairburn, GA 30213
 latitude: 33.5496124
@@ -4050,6 +4104,7 @@
           <t>chunk_type: identity
 company: continental tire the americas llc
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Barnesville, Lamar County</t>
         </is>
@@ -4127,6 +4182,7 @@
         <is>
           <t>chunk_type: location_employment
 company: continental tire the americas llc
+state: Georgia
 updated_location: Barnesville, Lamar County
 address: 160 Aldora St, Barnesville, GA 30204
 latitude: 33.0526972
@@ -4183,6 +4239,7 @@
           <t>chunk_type: identity
 company: daechang seat company
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Savannah, Chatham County</t>
         </is>
@@ -4260,6 +4317,7 @@
         <is>
           <t>chunk_type: location_employment
 company: daechang seat company
+state: Georgia
 updated_location: Savannah, Chatham County
 address: Savannah Chatham Manufacturing Center, Savannah, GA 31408
 latitude: 32.0841897
@@ -4316,6 +4374,7 @@
           <t>chunk_type: identity
 company: daehan solution georgia llc
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Covington, Henry County</t>
         </is>
@@ -4393,6 +4452,7 @@
         <is>
           <t>chunk_type: location_employment
 company: daehan solution georgia llc
+state: Georgia
 updated_location: Covington, Henry County
 address: 123 Industrial Blvd, Covington, GA 30014
 latitude: 33.4141149
@@ -4449,6 +4509,7 @@
           <t>chunk_type: identity
 company: daesol ausys
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Smyrna, Cobb County</t>
         </is>
@@ -4526,6 +4587,7 @@
         <is>
           <t>chunk_type: location_employment
 company: daesol ausys
+state: Georgia
 updated_location: Smyrna, Cobb County
 address: 2100 Lake Park Dr SE, Smyrna, GA 30080
 latitude: 33.8962818
@@ -4582,6 +4644,7 @@
           <t>chunk_type: identity
 company: daesol material georgia, llc
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Duluth, Gwinnett County</t>
         </is>
@@ -4659,6 +4722,7 @@
         <is>
           <t>chunk_type: location_employment
 company: daesol material georgia, llc
+state: Georgia
 updated_location: Duluth, Gwinnett County
 address: 2895 Old Norcross Rd, Duluth, GA 30096
 latitude: 33.9515466
@@ -4715,6 +4779,7 @@
           <t>chunk_type: identity
 company: daimler truck north america
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Covington, Newton County</t>
         </is>
@@ -4792,6 +4857,7 @@
         <is>
           <t>chunk_type: location_employment
 company: daimler truck north america
+state: Georgia
 updated_location: Covington, Newton County
 address: 7400 E Freeman Pkwy, Covington, GA 30014
 latitude: 33.5182052
@@ -4848,6 +4914,7 @@
           <t>chunk_type: identity
 company: das corp.
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Metter, Candler County</t>
         </is>
@@ -4925,6 +4992,7 @@
         <is>
           <t>chunk_type: location_employment
 company: das corp.
+state: Georgia
 updated_location: Metter, Candler County
 address: 730 Fortner Rd, Metter, GA 30439
 latitude: 32.3838336
@@ -4981,6 +5049,7 @@
           <t>chunk_type: identity
 company: decostar industries
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Buchanan, Polk County</t>
         </is>
@@ -5058,6 +5127,7 @@
         <is>
           <t>chunk_type: location_employment
 company: decostar industries
+state: Georgia
 updated_location: Buchanan, Polk County
 address: 219 Evans Dr, Buchanan, GA 30113
 latitude: 33.9059545
@@ -5114,6 +5184,7 @@
           <t>chunk_type: identity
 company: dekalb tool &amp; die inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Tucker, DeKalb County</t>
         </is>
@@ -5191,6 +5262,7 @@
         <is>
           <t>chunk_type: location_employment
 company: dekalb tool &amp; die inc.
+state: Georgia
 updated_location: Tucker, DeKalb County
 address: 2220 Stephens Dr, Tucker, GA 30084
 latitude: 33.849158
@@ -5247,6 +5319,7 @@
           <t>chunk_type: identity
 company: denkai america
 category: Tier 2/3
+state: Georgia
 industry_group: Rubber and Miscellaneous Plastic Products
 updated_location: Augusta, Richmond County</t>
         </is>
@@ -5324,6 +5397,7 @@
         <is>
           <t>chunk_type: location_employment
 company: denkai america
+state: Georgia
 updated_location: Augusta, Richmond County
 address: 1614 Douglas Rd, Augusta, GA 30906
 latitude: 33.4579269
@@ -5380,6 +5454,7 @@
           <t>chunk_type: identity
 company: denso manufacturing georgia
 category: Tier 2/3
+state: Georgia
 industry_group: Stone, Clay, Glass and Concrete Products
 updated_location: Pendergrass, Jackson County</t>
         </is>
@@ -5457,6 +5532,7 @@
         <is>
           <t>chunk_type: location_employment
 company: denso manufacturing georgia
+state: Georgia
 updated_location: Pendergrass, Jackson County
 address: 1000 Valentine Industrial Pkwy, Pendergrass, GA 30567
 latitude: 34.1800115
@@ -5513,6 +5589,7 @@
           <t>chunk_type: identity
 company: die-tech industries inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Stone, Clay, Glass and Concrete Products
 updated_location: Carrollton, Carroll County</t>
         </is>
@@ -5590,6 +5667,7 @@
         <is>
           <t>chunk_type: location_employment
 company: die-tech industries inc.
+state: Georgia
 updated_location: Carrollton, Carroll County
 address: 102 Automation Dr, Carrollton, GA 30117
 latitude: 33.6166214
@@ -5646,6 +5724,7 @@
           <t>chunk_type: identity
 company: dinex emissions inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Dublin, Laurens County</t>
         </is>
@@ -5723,6 +5802,7 @@
         <is>
           <t>chunk_type: location_employment
 company: dinex emissions inc.
+state: Georgia
 updated_location: Dublin, Laurens County
 address: 2020 Waldrep Industrial Blvd., Dublin, GA 31021
 latitude: 32.5138588
@@ -5779,6 +5859,7 @@
           <t>chunk_type: identity
 company: dongwon autopart technology georgia llc
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Hogansville, Meriwether County</t>
         </is>
@@ -5856,6 +5937,7 @@
         <is>
           <t>chunk_type: location_employment
 company: dongwon autopart technology georgia llc
+state: Georgia
 updated_location: Hogansville, Meriwether County
 address: 475 Meriwether Park Dr, Hogansville, GA 30230
 latitude: 33.1644618
@@ -5912,6 +5994,7 @@
           <t>chunk_type: identity
 company: dorsett industries inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Dalton, Whitfield County</t>
         </is>
@@ -5989,6 +6072,7 @@
         <is>
           <t>chunk_type: location_employment
 company: dorsett industries inc.
+state: Georgia
 updated_location: Dalton, Whitfield County
 address: 1304 May Street, Dalton, GA 30721
 latitude: 34.763633
@@ -6045,6 +6129,7 @@
           <t>chunk_type: identity
 company: down 2 earth trailers
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Baxley, Appling County</t>
         </is>
@@ -6122,6 +6207,7 @@
         <is>
           <t>chunk_type: location_employment
 company: down 2 earth trailers
+state: Georgia
 updated_location: Baxley, Appling County
 address: 1605 E Parker Street, Baxley, GA 31513
 latitude: 31.7707316
@@ -6178,6 +6264,7 @@
           <t>chunk_type: identity
 company: duckyang
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Braselton, Jackson County</t>
         </is>
@@ -6255,6 +6342,7 @@
         <is>
           <t>chunk_type: location_employment
 company: duckyang
+state: Georgia
 updated_location: Braselton, Jackson County
 address: 984 Broadway Avenue, Braselton, GA 30517
 latitude: 34.106234
@@ -6311,6 +6399,7 @@
           <t>chunk_type: identity
 company: eaton corp.
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Athens, Clarke County</t>
         </is>
@@ -6388,6 +6477,7 @@
         <is>
           <t>chunk_type: location_employment
 company: eaton corp.
+state: Georgia
 updated_location: Athens, Clarke County
 address: 695 Indian Hills Road, Athens, GA 30601
 latitude: 33.9664651
@@ -6444,6 +6534,7 @@
           <t>chunk_type: identity
 company: ecoplastic america corporation
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Register, Bulloch County</t>
         </is>
@@ -6521,6 +6612,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ecoplastic america corporation
+state: Georgia
 updated_location: Register, Bulloch County
 address: 4800 Highway 301 S., Register, GA 30452
 latitude: 32.3288665
@@ -6577,6 +6669,7 @@
           <t>chunk_type: identity
 company: ecoplastic corporation
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Statesboro, Bulloch County</t>
         </is>
@@ -6654,6 +6747,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ecoplastic corporation
+state: Georgia
 updated_location: Statesboro, Bulloch County
 address: 25 Siebald St, Statesboro, GA 30458
 latitude: 32.4500733
@@ -6710,6 +6804,7 @@
           <t>chunk_type: identity
 company: elan technology inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Midway, Liberty County</t>
         </is>
@@ -6787,6 +6882,7 @@
         <is>
           <t>chunk_type: location_employment
 company: elan technology inc.
+state: Georgia
 updated_location: Midway, Liberty County
 address: 169 Elan Court, Midway, GA 31320
 latitude: 31.7958661
@@ -6843,6 +6939,7 @@
           <t>chunk_type: identity
 company: enchem america inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Commerce, Jackson County</t>
         </is>
@@ -6920,6 +7017,7 @@
         <is>
           <t>chunk_type: location_employment
 company: enchem america inc.
+state: Georgia
 updated_location: Commerce, Jackson County
 address: 648 Highway 334, Commerce, GA 30530
 latitude: 34.1720636
@@ -6976,6 +7074,7 @@
           <t>chunk_type: identity
 company: enplas usa inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Marietta, Cobb County</t>
         </is>
@@ -7053,6 +7152,7 @@
         <is>
           <t>chunk_type: location_employment
 company: enplas usa inc.
+state: Georgia
 updated_location: Marietta, Cobb County
 address: 1901 West Oak Circle, Marietta, GA 30062
 latitude: 33.9867797
@@ -7109,6 +7209,7 @@
           <t>chunk_type: identity
 company: erdrich usa inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Dublin, Laurens County</t>
         </is>
@@ -7186,6 +7287,7 @@
         <is>
           <t>chunk_type: location_employment
 company: erdrich usa inc.
+state: Georgia
 updated_location: Dublin, Laurens County
 address: 112 Willie Paulk Parkway, Dublin, GA 31021
 latitude: 32.5001482
@@ -7242,6 +7344,7 @@
           <t>chunk_type: identity
 company: evco plastics
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Calhoun, Gordon County</t>
         </is>
@@ -7319,6 +7422,7 @@
         <is>
           <t>chunk_type: location_employment
 company: evco plastics
+state: Georgia
 updated_location: Calhoun, Gordon County
 address: 100 EVCO Drive, Calhoun, GA 30701
 latitude: 34.4455959
@@ -7375,6 +7479,7 @@
           <t>chunk_type: identity
 company: f&amp;p georgia manufacturing
 category: Tier 1/2
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Rome, Floyd County</t>
         </is>
@@ -7452,6 +7557,7 @@
         <is>
           <t>chunk_type: location_employment
 company: f&amp;p georgia manufacturing
+state: Georgia
 updated_location: Rome, Floyd County
 address: 88 Enterprise Drive SE, Rome, GA 30161
 latitude: 34.1708696
@@ -7508,6 +7614,7 @@
           <t>chunk_type: identity
 company: fanello industries inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Lavonia, Franklin County</t>
         </is>
@@ -7585,6 +7692,7 @@
         <is>
           <t>chunk_type: location_employment
 company: fanello industries inc.
+state: Georgia
 updated_location: Lavonia, Franklin County
 address: 50 E Main Street, Lavonia, GA 30553
 latitude: 34.4200267
@@ -7641,6 +7749,7 @@
           <t>chunk_type: identity
 company: first american resources
 category: Tier 2/3
+state: Georgia
 industry_group: Primary Metal Industries
 updated_location: Mableton, Cobb County</t>
         </is>
@@ -7718,6 +7827,7 @@
         <is>
           <t>chunk_type: location_employment
 company: first american resources
+state: Georgia
 updated_location: Mableton, Cobb County
 address: 2030 Riverview Industrial Dr SE, Mableton, GA 30126
 latitude: 33.8131088
@@ -7774,6 +7884,7 @@
           <t>chunk_type: identity
 company: flambeau inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Madison, Morgan County</t>
         </is>
@@ -7851,6 +7962,7 @@
         <is>
           <t>chunk_type: location_employment
 company: flambeau inc.
+state: Georgia
 updated_location: Madison, Morgan County
 address: 1330 Atlanta Highway, Madison, GA 30650
 latitude: 33.5804884
@@ -7907,6 +8019,7 @@
           <t>chunk_type: identity
 company: fouts brothers fire equipment
 category: Tier 1/2
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Milledgeville, Baldwin County</t>
         </is>
@@ -7984,6 +8097,7 @@
         <is>
           <t>chunk_type: location_employment
 company: fouts brothers fire equipment
+state: Georgia
 updated_location: Milledgeville, Baldwin County
 address: 138 Roberson Mill Rd, Milledgeville, GA 31061
 latitude: 33.1040128
@@ -8040,6 +8154,7 @@
           <t>chunk_type: identity
 company: fox factory
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Duluth, Gwinnett County</t>
         </is>
@@ -8117,6 +8232,7 @@
         <is>
           <t>chunk_type: location_employment
 company: fox factory
+state: Georgia
 updated_location: Duluth, Gwinnett County
 address: 2055 Sugarloaf Circle, Suite 300, Duluth, GA 30097
 latitude: 33.9864549
@@ -8173,6 +8289,7 @@
           <t>chunk_type: identity
 company: freudenberg-nok
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: LaGrange, Troup County</t>
         </is>
@@ -8250,6 +8367,7 @@
         <is>
           <t>chunk_type: location_employment
 company: freudenberg-nok
+state: Georgia
 updated_location: LaGrange, Troup County
 address: 1618 Lukken Industrial Dr, LaGrange, GA 30240
 latitude: 33.0137815
@@ -8306,6 +8424,7 @@
           <t>chunk_type: identity
 company: freudenberg-nok
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: LaGrange, Troup County</t>
         </is>
@@ -8383,6 +8502,7 @@
         <is>
           <t>chunk_type: location_employment
 company: freudenberg-nok
+state: Georgia
 updated_location: LaGrange, Troup County
 address: 1618 Lukken Industrial Dr, LaGrange, GA 30240
 latitude: 33.0137815
@@ -8439,6 +8559,7 @@
           <t>chunk_type: identity
 company: freyr battery
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Atlanta, Fulton County</t>
         </is>
@@ -8516,6 +8637,7 @@
         <is>
           <t>chunk_type: location_employment
 company: freyr battery
+state: Georgia
 updated_location: Atlanta, Fulton County
 address: 601 10th St NW, Suite 400, Atlanta, GA 30318
 latitude: 33.7817149
@@ -8572,6 +8694,7 @@
           <t>chunk_type: identity
 company: gedia georgia llc
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Dalton, Fulton County</t>
         </is>
@@ -8649,6 +8772,7 @@
         <is>
           <t>chunk_type: location_employment
 company: gedia georgia llc
+state: Georgia
 updated_location: Dalton, Fulton County
 address: 1 GEDIA Way, Dalton, GA 30721
 latitude: 33.7822022
@@ -8705,6 +8829,7 @@
           <t>chunk_type: identity
 company: global powertrain systems llc
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Jefferson, Jackson County</t>
         </is>
@@ -8782,6 +8907,7 @@
         <is>
           <t>chunk_type: location_employment
 company: global powertrain systems llc
+state: Georgia
 updated_location: Jefferson, Jackson County
 address: 300 Logistics Parkway, Jefferson, GA 30549
 latitude: 34.1890046
@@ -8838,6 +8964,7 @@
           <t>chunk_type: identity
 company: glovis georgia llc
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Savannah, Chatham County</t>
         </is>
@@ -8915,6 +9042,7 @@
         <is>
           <t>chunk_type: location_employment
 company: glovis georgia llc
+state: Georgia
 updated_location: Savannah, Chatham County
 address: 127 N Park Ct, Savannah, GA 31407
 latitude: 32.231682
@@ -8971,6 +9099,7 @@
           <t>chunk_type: identity
 company: goodyear tire &amp; rubber co.
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Atlanta, Clayton County</t>
         </is>
@@ -9048,6 +9177,7 @@
         <is>
           <t>chunk_type: location_employment
 company: goodyear tire &amp; rubber co.
+state: Georgia
 updated_location: Atlanta, Clayton County
 address: 1420 Phoenix Blvd, Suite 300, Atlanta, GA 30349
 latitude: 33.6143207
@@ -9104,6 +9234,7 @@
           <t>chunk_type: identity
 company: great dane lp
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Savannah, Chatham County</t>
         </is>
@@ -9181,6 +9312,7 @@
         <is>
           <t>chunk_type: location_employment
 company: great dane lp
+state: Georgia
 updated_location: Savannah, Chatham County
 address: 602 E Lathrop Ave, Savannah, GA 31415
 latitude: 32.0869786
@@ -9237,6 +9369,7 @@
           <t>chunk_type: identity
 company: great dane trailers
 category: Tier 2/3
+state: Georgia
 industry_group: Fabricated Metal Products
 updated_location: Savannah, Chatham County</t>
         </is>
@@ -9314,6 +9447,7 @@
         <is>
           <t>chunk_type: location_employment
 company: great dane trailers
+state: Georgia
 updated_location: Savannah, Chatham County
 address: 602 E Lathrop Ave, Savannah, GA 31415
 latitude: 32.0869786
@@ -9370,6 +9504,7 @@
           <t>chunk_type: identity
 company: grudem
 category: Tier 2/3
+state: Georgia
 industry_group: Machinery Except Electrical
 updated_location: Gainesville, Hall County</t>
         </is>
@@ -9447,6 +9582,7 @@
         <is>
           <t>chunk_type: location_employment
 company: grudem
+state: Georgia
 updated_location: Gainesville, Hall County
 address: 1245 Industrial Blvd, Gainesville, GA 30501
 latitude: 34.2762316
@@ -9503,6 +9639,7 @@
           <t>chunk_type: identity
 company: gsc steel stamping llc
 category: Tier 2/3
+state: Georgia
 industry_group: Machinery Except Electrical
 updated_location: Adairsville, Bartow County</t>
         </is>
@@ -9580,6 +9717,7 @@
         <is>
           <t>chunk_type: location_employment
 company: gsc steel stamping llc
+state: Georgia
 updated_location: Adairsville, Bartow County
 address: 104 International Pkwy, Adairsville, GA 30103
 latitude: 34.3845755
@@ -9636,6 +9774,7 @@
           <t>chunk_type: identity
 company: haering precision usa lp
 category: Tier 2/3
+state: Georgia
 industry_group: Machinery Except Electrical
 updated_location: Buford, Hall County</t>
         </is>
@@ -9713,6 +9852,7 @@
         <is>
           <t>chunk_type: location_employment
 company: haering precision usa lp
+state: Georgia
 updated_location: Buford, Hall County
 address: 5000 Frontage Rd, Buford, GA 30518
 latitude: 34.2328208
@@ -9769,6 +9909,7 @@
           <t>chunk_type: identity
 company: haering precision usa lp
 category: Tier 2/3
+state: Georgia
 industry_group: Machinery Except Electrical
 updated_location: Buford, Hall County</t>
         </is>
@@ -9846,6 +9987,7 @@
         <is>
           <t>chunk_type: location_employment
 company: haering precision usa lp
+state: Georgia
 updated_location: Buford, Hall County
 address: 5000 Frontage Rd, Buford, GA 30518
 latitude: 34.2328208
@@ -9902,6 +10044,7 @@
           <t>chunk_type: identity
 company: hanon systems usa llc
 category: Tier 2/3
+state: Alabama
 industry_group: Machinery Except Electrical
 updated_location: Shorter, Harris County</t>
         </is>
@@ -9979,6 +10122,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hanon systems usa llc
+state: Alabama
 updated_location: Shorter, Harris County
 address: 400 Hanon Dr, Shorter, GA 36075
 latitude: 32.4705166
@@ -10035,6 +10179,7 @@
           <t>chunk_type: identity
 company: hella automotive sales inc.
 category: Tier 2/3
+state: Georgia
 industry_group: Machinery Except Electrical
 updated_location: Atlanta, Cobb County</t>
         </is>
@@ -10112,6 +10257,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hella automotive sales inc.
+state: Georgia
 updated_location: Atlanta, Cobb County
 address: 2018 Powers Ferry Rd SE, Suite 400, Atlanta, GA 30339
 latitude: 33.9022104
@@ -10168,6 +10314,7 @@
           <t>chunk_type: identity
 company: hexpol compounding corp.
 category: Tier 2/3
+state: Georgia
 industry_group: Machinery Except Electrical
 updated_location: Griffin, Spalding County</t>
         </is>
@@ -10245,6 +10392,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hexpol compounding corp.
+state: Georgia
 updated_location: Griffin, Spalding County
 address: 1020 Plantation Way, Griffin, GA 30224
 latitude: 33.2928001
@@ -10301,6 +10449,7 @@
           <t>chunk_type: identity
 company: hitachi astemo
 category: Tier 1/2
+state: Alabama
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Shorter, Harris County</t>
         </is>
@@ -10378,6 +10527,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hitachi astemo
+state: Alabama
 updated_location: Shorter, Harris County
 address: 400 Hanon Dr, Shorter, GA 36075
 latitude: 32.4705166
@@ -10434,6 +10584,7 @@
           <t>chunk_type: identity
 company: hitachi astemo americas inc.
 category: Tier 1/2
+state: Alabama
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Shorter, Harris County</t>
         </is>
@@ -10511,6 +10662,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hitachi astemo americas inc.
+state: Alabama
 updated_location: Shorter, Harris County
 address: 400 Hanon Dr, Shorter, GA 36075
 latitude: 32.4705166
@@ -10567,6 +10719,7 @@
           <t>chunk_type: identity
 company: hollingsworth &amp; vose co.
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Hawkinsville, Pulaski County</t>
         </is>
@@ -10644,6 +10797,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hollingsworth &amp; vose co.
+state: Georgia
 updated_location: Hawkinsville, Pulaski County
 address: 111 Hollingsworth &amp; Vose Rd, Hawkinsville, GA 31036
 latitude: 32.2835422
@@ -10700,6 +10854,7 @@
           <t>chunk_type: identity
 company: honda development &amp; manufacturing
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Tallapoosa, Cherokee County</t>
         </is>
@@ -10777,6 +10932,7 @@
         <is>
           <t>chunk_type: location_employment
 company: honda development &amp; manufacturing
+state: Georgia
 updated_location: Tallapoosa, Cherokee County
 address: 1000 Honda Dr, Tallapoosa, GA 30176
 latitude: 34.2575874
@@ -10833,6 +10989,7 @@
           <t>chunk_type: identity
 company: hwashin
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: LaGrange, Haralson County</t>
         </is>
@@ -10910,6 +11067,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hwashin
+state: Georgia
 updated_location: LaGrange, Haralson County
 address: 1465 Troup Industrial Blvd, LaGrange, GA 30240
 latitude: 33.6931709
@@ -10966,6 +11124,7 @@
           <t>chunk_type: identity
 company: hyundai &amp; lg energy solution (lges)
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Ellabell, Chatham County</t>
         </is>
@@ -11043,6 +11202,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hyundai &amp; lg energy solution (lges)
+state: Georgia
 updated_location: Ellabell, Chatham County
 address: 700 Hyundai Blvd, Ellabell, GA 31308
 latitude: 22.093612
@@ -11099,6 +11259,7 @@
           <t>chunk_type: identity
 company: hyundai industrial co.
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Ellabell, Chatham County</t>
         </is>
@@ -11176,6 +11337,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hyundai industrial co.
+state: Georgia
 updated_location: Ellabell, Chatham County
 address: 700 Hyundai Blvd, Ellabell, GA 31308
 latitude: 22.093612
@@ -11232,6 +11394,7 @@
           <t>chunk_type: identity
 company: hyundai mobis (georgia)
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: West Point, Troup County</t>
         </is>
@@ -11309,6 +11472,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hyundai mobis (georgia)
+state: Georgia
 updated_location: West Point, Troup County
 address: 300 Hyundai MOBIS Dr, West Point, GA 31833
 latitude: 32.8772531
@@ -11365,6 +11529,7 @@
           <t>chunk_type: identity
 company: hyundai motor group
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Ellabell, Bryan County</t>
         </is>
@@ -11442,6 +11607,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hyundai motor group
+state: Georgia
 updated_location: Ellabell, Bryan County
 address: 700 Hyundai Blvd, Ellabell, GA 31308
 latitude: 32.159233
@@ -11498,6 +11664,7 @@
           <t>chunk_type: identity
 company: hyundai transys georgia powertrain
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: West Point, Troup County</t>
         </is>
@@ -11575,6 +11742,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hyundai transys georgia powertrain
+state: Georgia
 updated_location: West Point, Troup County
 address: 100 Powertrain Way, West Point, GA 31833
 latitude: 32.903183
@@ -11631,6 +11799,7 @@
           <t>chunk_type: identity
 company: hyundai transys georgia seating systems
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: West Point, Troup County</t>
         </is>
@@ -11708,6 +11877,7 @@
         <is>
           <t>chunk_type: location_employment
 company: hyundai transys georgia seating systems
+state: Georgia
 updated_location: West Point, Troup County
 address: 801 Transys Pkwy, West Point, GA 31833
 latitude: 32.8772531
@@ -11764,6 +11934,7 @@
           <t>chunk_type: identity
 company: immi
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Dublin, Laurens County</t>
         </is>
@@ -11841,6 +12012,7 @@
         <is>
           <t>chunk_type: location_employment
 company: immi
+state: Georgia
 updated_location: Dublin, Laurens County
 address: 2002 Industrial Park Dr, Dublin, GA 31021
 latitude: 32.511763
@@ -11897,6 +12069,7 @@
           <t>chunk_type: identity
 company: ims gear georgia inc.
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Suwanee, Gwinnett County</t>
         </is>
@@ -11974,6 +12147,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ims gear georgia inc.
+state: Georgia
 updated_location: Suwanee, Gwinnett County
 address: 300 Satellite Blvd NE, Suwanee, GA 30024
 latitude: 34.035115
@@ -12030,6 +12204,7 @@
           <t>chunk_type: identity
 company: inalfa roof systems inc.
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Acworth, Cobb County</t>
         </is>
@@ -12107,6 +12282,7 @@
         <is>
           <t>chunk_type: location_employment
 company: inalfa roof systems inc.
+state: Georgia
 updated_location: Acworth, Cobb County
 address: 100 Inalfa Dr, Acworth, GA 30102
 latitude: 34.07068
@@ -12163,6 +12339,7 @@
           <t>chunk_type: identity
 company: jac products inc.
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Jefferson, Jackson County</t>
         </is>
@@ -12240,6 +12417,7 @@
         <is>
           <t>chunk_type: location_employment
 company: jac products inc.
+state: Georgia
 updated_location: Jefferson, Jackson County
 address: 120 Logistics Pkwy, Jefferson, GA 30549
 latitude: 34.10601
@@ -12296,6 +12474,7 @@
           <t>chunk_type: identity
 company: jefferson southern corp.
 category: Tier 1/2
+state: Georgia
 industry_group: Electronic and Other Electrical Equipment and Components
 updated_location: Commerce, Forsyth County</t>
         </is>
@@ -12373,6 +12552,7 @@
         <is>
           <t>chunk_type: location_employment
 company: jefferson southern corp.
+state: Georgia
 updated_location: Commerce, Forsyth County
 address: 1 Jefferson Southern Dr, Commerce, GA 30529
 latitude: 34.197573
@@ -12429,6 +12609,7 @@
           <t>chunk_type: identity
 company: jefferson southern corporation
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Commerce, Forsyth County</t>
         </is>
@@ -12506,6 +12687,7 @@
         <is>
           <t>chunk_type: location_employment
 company: jefferson southern corporation
+state: Georgia
 updated_location: Commerce, Forsyth County
 address: 1 Jefferson Southern Dr, Commerce, GA 30529
 latitude: 34.197573
@@ -12562,6 +12744,7 @@
           <t>chunk_type: identity
 company: joon georgia, inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: West Point, Chattahoochee County</t>
         </is>
@@ -12639,6 +12822,7 @@
         <is>
           <t>chunk_type: location_employment
 company: joon georgia, inc.
+state: Georgia
 updated_location: West Point, Chattahoochee County
 address: 100 Industrial Park Rd, West Point, GA 31833
 latitude: 32.314089
@@ -12695,6 +12879,7 @@
           <t>chunk_type: identity
 company: jtekt north america corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Pendergrass, Jackson County</t>
         </is>
@@ -12772,6 +12957,7 @@
         <is>
           <t>chunk_type: location_employment
 company: jtekt north america corp.
+state: Georgia
 updated_location: Pendergrass, Jackson County
 address: 301 Teco Dr, Pendergrass, GA 30567
 latitude: 34.130329
@@ -12828,6 +13014,7 @@
           <t>chunk_type: identity
 company: kautex inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Lavonia, Rabun County</t>
         </is>
@@ -12905,6 +13092,7 @@
         <is>
           <t>chunk_type: location_employment
 company: kautex inc.
+state: Georgia
 updated_location: Lavonia, Rabun County
 address: 100 Kautex Dr, Lavonia, GA 30553
 latitude: 34.968226
@@ -12961,6 +13149,7 @@
           <t>chunk_type: identity
 company: kia georgia inc.
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: West Point, Troup County</t>
         </is>
@@ -13038,6 +13227,7 @@
         <is>
           <t>chunk_type: location_employment
 company: kia georgia inc.
+state: Georgia
 updated_location: West Point, Troup County
 address: 1025 Kia Blvd, West Point, GA 31833
 latitude: 32.9322549
@@ -13094,6 +13284,7 @@
           <t>chunk_type: identity
 company: ktx america corporation
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: LaGrange, Meriwether County</t>
         </is>
@@ -13171,6 +13362,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ktx america corporation
+state: Georgia
 updated_location: LaGrange, Meriwether County
 address: 205 KTX Dr, LaGrange, GA 30240
 latitude: 33.163387
@@ -13227,6 +13419,7 @@
           <t>chunk_type: identity
 company: kumho tire usa inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Macon, Bibb County</t>
         </is>
@@ -13304,6 +13497,7 @@
         <is>
           <t>chunk_type: location_employment
 company: kumho tire usa inc.
+state: Georgia
 updated_location: Macon, Bibb County
 address: 1 Kumho Dr, Macon, GA 31216
 latitude: 32.8406946
@@ -13360,6 +13554,7 @@
           <t>chunk_type: identity
 company: kyungshin america corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: West Point, Troup County</t>
         </is>
@@ -13437,6 +13632,7 @@
         <is>
           <t>chunk_type: location_employment
 company: kyungshin america corp.
+state: Georgia
 updated_location: West Point, Troup County
 address: 85 Kyungshin Dr, West Point, GA 31833
 latitude: 32.8772531
@@ -13493,6 +13689,7 @@
           <t>chunk_type: identity
 company: lark united manufacturing inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Dublin, Laurens County</t>
         </is>
@@ -13570,6 +13767,7 @@
         <is>
           <t>chunk_type: location_employment
 company: lark united manufacturing inc.
+state: Georgia
 updated_location: Dublin, Laurens County
 address: 200 Industrial Blvd, Dublin, GA 31021
 latitude: 32.5320682
@@ -13626,6 +13824,7 @@
           <t>chunk_type: identity
 company: lear corporation
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Hammond Industrial Park, Troup County</t>
         </is>
@@ -13703,6 +13902,7 @@
         <is>
           <t>chunk_type: location_employment
 company: lear corporation
+state: Georgia
 updated_location: Hammond Industrial Park, Troup County
 address: 100 Lear Dr, Hammond Industrial Park, GA 30240
 latitude: 33.051868
@@ -13759,6 +13959,7 @@
           <t>chunk_type: identity
 company: lehigh technologies inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Tucker, Walton County</t>
         </is>
@@ -13836,6 +14037,7 @@
         <is>
           <t>chunk_type: location_employment
 company: lehigh technologies inc.
+state: Georgia
 updated_location: Tucker, Walton County
 address: 1000 New Horizons Way, Tucker, GA 30084
 latitude: 33.760895
@@ -13892,6 +14094,7 @@
           <t>chunk_type: identity
 company: linde + wiemann
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Dublin, Laurens County</t>
         </is>
@@ -13969,6 +14172,7 @@
         <is>
           <t>chunk_type: location_employment
 company: linde + wiemann
+state: Georgia
 updated_location: Dublin, Laurens County
 address: 200 Linde Wiemann Way, Dublin, GA 31021
 latitude: 32.493414
@@ -14025,6 +14229,7 @@
           <t>chunk_type: identity
 company: lund international inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Madison, Morgan County</t>
         </is>
@@ -14102,6 +14307,7 @@
         <is>
           <t>chunk_type: location_employment
 company: lund international inc.
+state: Georgia
 updated_location: Madison, Morgan County
 address: 189 Excalibur Dr, Madison, GA 30650
 latitude: 33.589481
@@ -14158,6 +14364,7 @@
           <t>chunk_type: identity
 company: lund international inc./ventshade division
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Madison, Morgan County</t>
         </is>
@@ -14235,6 +14442,7 @@
         <is>
           <t>chunk_type: location_employment
 company: lund international inc./ventshade division
+state: Georgia
 updated_location: Madison, Morgan County
 address: 189 Excalibur Dr, Madison, GA 30650
 latitude: 33.589481
@@ -14291,6 +14499,7 @@
           <t>chunk_type: identity
 company: lyle industries inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Dawsonville, Dawson County</t>
         </is>
@@ -14368,6 +14577,7 @@
         <is>
           <t>chunk_type: location_employment
 company: lyle industries inc.
+state: Georgia
 updated_location: Dawsonville, Dawson County
 address: 715 Lyle Industrial Dr, Dawsonville, GA 30534
 latitude: 34.3593919607897
@@ -14424,6 +14634,7 @@
           <t>chunk_type: identity
 company: lyle industries inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Dawsonville, Dawson County</t>
         </is>
@@ -14501,6 +14712,7 @@
         <is>
           <t>chunk_type: location_employment
 company: lyle industries inc.
+state: Georgia
 updated_location: Dawsonville, Dawson County
 address: 715 Lyle Industrial Dr, Dawsonville, GA 30534
 latitude: 34.3589668332603
@@ -14557,6 +14769,7 @@
           <t>chunk_type: identity
 company: mack trucks
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Dublin, Lowndes County</t>
         </is>
@@ -14634,6 +14847,7 @@
         <is>
           <t>chunk_type: location_employment
 company: mack trucks
+state: Georgia
 updated_location: Dublin, Lowndes County
 address: 1525 Madison Hwy, Dublin, GA 31021
 latitude: 30.804784
@@ -14690,6 +14904,7 @@
           <t>chunk_type: identity
 company: magna international
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Carrollton, Carroll County</t>
         </is>
@@ -14767,6 +14982,7 @@
         <is>
           <t>chunk_type: location_employment
 company: magna international
+state: Georgia
 updated_location: Carrollton, Carroll County
 address: 250 Magna Dr, Carrollton, GA 30117
 latitude: 33.574772
@@ -14823,6 +15039,7 @@
           <t>chunk_type: identity
 company: mando america corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Hogansville, Meriwether County</t>
         </is>
@@ -14900,6 +15117,7 @@
         <is>
           <t>chunk_type: location_employment
 company: mando america corp.
+state: Georgia
 updated_location: Hogansville, Meriwether County
 address: 100 Mando Dr, Hogansville, GA 30230
 latitude: 33.1709673066386
@@ -14956,6 +15174,7 @@
           <t>chunk_type: identity
 company: master craft engineering inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Lavonia, Franklin County</t>
         </is>
@@ -15033,6 +15252,7 @@
         <is>
           <t>chunk_type: location_employment
 company: master craft engineering inc.
+state: Georgia
 updated_location: Lavonia, Franklin County
 address: 1000 Mastercraft Ln, Lavonia, GA 30553
 latitude: 34.408031
@@ -15089,6 +15309,7 @@
           <t>chunk_type: identity
 company: mat heavy duty
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Suwanee, Gwinnett County</t>
         </is>
@@ -15166,6 +15387,7 @@
         <is>
           <t>chunk_type: location_employment
 company: mat heavy duty
+state: Georgia
 updated_location: Suwanee, Gwinnett County
 address: 555 Satellite Blvd NW, Suwanee, GA 30024
 latitude: 34.0278743
@@ -15222,6 +15444,7 @@
           <t>chunk_type: identity
 company: maxxis international usa
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Suwanee, Clayton County</t>
         </is>
@@ -15299,6 +15522,7 @@
         <is>
           <t>chunk_type: location_employment
 company: maxxis international usa
+state: Georgia
 updated_location: Suwanee, Clayton County
 address: 100 International Pkwy, Suwanee, GA 30024
 latitude: 33.6352704
@@ -15355,6 +15579,7 @@
           <t>chunk_type: identity
 company: mercedes-benz usa llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Sandy Springs, Fulton County</t>
         </is>
@@ -15432,6 +15657,7 @@
         <is>
           <t>chunk_type: location_employment
 company: mercedes-benz usa llc
+state: Georgia
 updated_location: Sandy Springs, Fulton County
 address: 1 Mercedes-Benz Dr, Sandy Springs, GA 30328
 latitude: 33.9345221674192
@@ -15488,6 +15714,7 @@
           <t>chunk_type: identity
 company: michelin tread technologies
 category: Tier 1
+state: South Carolina
 industry_group: Transportation Equipment
 updated_location: Hart County</t>
         </is>
@@ -15565,6 +15792,7 @@
         <is>
           <t>chunk_type: location_employment
 company: michelin tread technologies
+state: South Carolina
 updated_location: Hart County
 address: 1 Parkway South Blvd, Greenville, SC 29615
 latitude: 34.8611177082749
@@ -15621,6 +15849,7 @@
           <t>chunk_type: identity
 company: milliken &amp; co./valway plant
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: LaGrange, Troup County</t>
         </is>
@@ -15698,6 +15927,7 @@
         <is>
           <t>chunk_type: location_employment
 company: milliken &amp; co./valway plant
+state: Georgia
 updated_location: LaGrange, Troup County
 address: 920 Milliken Rd, LaGrange, GA 30241
 latitude: 33.050989
@@ -15754,6 +15984,7 @@
           <t>chunk_type: identity
 company: minebea accesssolutions usa inc.
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Gainesville, Fulton County</t>
         </is>
@@ -15831,6 +16062,7 @@
         <is>
           <t>chunk_type: location_employment
 company: minebea accesssolutions usa inc.
+state: Georgia
 updated_location: Gainesville, Fulton County
 address: 200 Access Way, Gainesville, GA 30501
 latitude: 33.7654713
@@ -15887,6 +16119,7 @@
           <t>chunk_type: identity
 company: mobis alabama llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: West Point, Troup County</t>
         </is>
@@ -15964,6 +16197,7 @@
         <is>
           <t>chunk_type: location_employment
 company: mobis alabama llc
+state: Georgia
 updated_location: West Point, Troup County
 address: 300 Hyundai MOBIS Dr, West Point, GA 31833
 latitude: 32.9150013591105
@@ -16020,6 +16254,7 @@
           <t>chunk_type: identity
 company: mollertech llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Dalton, Whitfield County</t>
         </is>
@@ -16097,6 +16332,7 @@
         <is>
           <t>chunk_type: location_employment
 company: mollertech llc
+state: Georgia
 updated_location: Dalton, Whitfield County
 address: 100 Mollertech Dr, Dalton, GA 30721
 latitude: 34.788493
@@ -16153,6 +16389,7 @@
           <t>chunk_type: identity
 company: morgan corp.
 category: Tier 1
+state: North Carolina
 industry_group: Transportation Equipment
 updated_location: Rabun County</t>
         </is>
@@ -16230,6 +16467,7 @@
         <is>
           <t>chunk_type: location_employment
 company: morgan corp.
+state: North Carolina
 updated_location: Rabun County
 address: 15 Morgan Center Dr, Morganton, NC 28655
 latitude: 35.754058
@@ -16286,6 +16524,7 @@
           <t>chunk_type: identity
 company: murata electronics north america inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Smyrna, Paulding County</t>
         </is>
@@ -16363,6 +16602,7 @@
         <is>
           <t>chunk_type: location_employment
 company: murata electronics north america inc.
+state: Georgia
 updated_location: Smyrna, Paulding County
 address: 1000 Corporate Dr, Smyrna, GA 30080
 latitude: 33.8866538
@@ -16419,6 +16659,7 @@
           <t>chunk_type: identity
 company: neaton rome inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Rome, Douglas County</t>
         </is>
@@ -16496,6 +16737,7 @@
         <is>
           <t>chunk_type: location_employment
 company: neaton rome inc.
+state: Georgia
 updated_location: Rome, Douglas County
 address: 1 Neaton Dr, Rome, GA 30161
 latitude: 33.766217
@@ -16552,6 +16794,7 @@
           <t>chunk_type: identity
 company: nidec elesys americas corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Suwanee, Forsyth County</t>
         </is>
@@ -16629,6 +16872,7 @@
         <is>
           <t>chunk_type: location_employment
 company: nidec elesys americas corp.
+state: Georgia
 updated_location: Suwanee, Forsyth County
 address: 3900 Lakefield Ct, Suwanee, GA 30024
 latitude: 34.064876
@@ -16685,6 +16929,7 @@
           <t>chunk_type: identity
 company: nifco ktw america corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Toccoa, Stephens County</t>
         </is>
@@ -16762,6 +17007,7 @@
         <is>
           <t>chunk_type: location_employment
 company: nifco ktw america corp.
+state: Georgia
 updated_location: Toccoa, Stephens County
 address: 100 Nifco Way, Toccoa, GA 30577
 latitude: 34.5179964289089
@@ -16818,6 +17064,7 @@
           <t>chunk_type: identity
 company: nile automotive
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Cumming, Forsyth County</t>
         </is>
@@ -16895,6 +17142,7 @@
         <is>
           <t>chunk_type: location_employment
 company: nile automotive
+state: Georgia
 updated_location: Cumming, Forsyth County
 address: 4490 Alicia Lane, Cumming, GA 30028
 latitude: 34.2861491093215
@@ -16951,6 +17199,7 @@
           <t>chunk_type: identity
 company: nisshinbo automotive manufacturing inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Covington, Newton County</t>
         </is>
@@ -17028,6 +17277,7 @@
         <is>
           <t>chunk_type: location_employment
 company: nisshinbo automotive manufacturing inc.
+state: Georgia
 updated_location: Covington, Newton County
 address: 14187 Nisshinbo Drive, Covington, GA 30014
 latitude: 33.627596641273
@@ -17084,6 +17334,7 @@
           <t>chunk_type: identity
 company: nivel parts &amp; manufacturing co. llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Cairo, Grady County</t>
         </is>
@@ -17161,6 +17412,7 @@
         <is>
           <t>chunk_type: location_employment
 company: nivel parts &amp; manufacturing co. llc
+state: Georgia
 updated_location: Cairo, Grady County
 address: 2051 2nd Ave NE, Cairo, GA 39828
 latitude: 30.8796091793369
@@ -17217,6 +17469,7 @@
           <t>chunk_type: identity
 company: novelis inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Atlanta, Fulton County</t>
         </is>
@@ -17294,6 +17547,7 @@
         <is>
           <t>chunk_type: location_employment
 company: novelis inc.
+state: Georgia
 updated_location: Atlanta, Fulton County
 address: 3560 Lenox Rd NE, Suite 2000, Atlanta, GA 30326
 latitude: 33.8540394890331
@@ -17350,6 +17604,7 @@
           <t>chunk_type: identity
 company: novelis inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Atlanta, Fulton County</t>
         </is>
@@ -17427,6 +17682,7 @@
         <is>
           <t>chunk_type: location_employment
 company: novelis inc.
+state: Georgia
 updated_location: Atlanta, Fulton County
 address: 3560 Lenox Rd NE, Suite 2000, Atlanta, GA 30326
 latitude: 33.8542055150128
@@ -17483,6 +17739,7 @@
           <t>chunk_type: identity
 company: novelis inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Atlanta, Fulton County</t>
         </is>
@@ -17560,6 +17817,7 @@
         <is>
           <t>chunk_type: location_employment
 company: novelis inc.
+state: Georgia
 updated_location: Atlanta, Fulton County
 address: 3560 Lenox Rd NE, Suite 2000, Atlanta, GA 30326
 latitude: 33.8541642345505
@@ -17616,6 +17874,7 @@
           <t>chunk_type: identity
 company: nvh korea
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Locust Grove, Henry County</t>
         </is>
@@ -17693,6 +17952,7 @@
         <is>
           <t>chunk_type: location_employment
 company: nvh korea
+state: Georgia
 updated_location: Locust Grove, Henry County
 address: 120 Colvin Drive, Locust Grove, GA 30248
 latitude: 33.3690335423479
@@ -17749,6 +18009,7 @@
           <t>chunk_type: identity
 company: oneda corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Gainesville, Hall County</t>
         </is>
@@ -17826,6 +18087,7 @@
         <is>
           <t>chunk_type: location_employment
 company: oneda corp.
+state: Georgia
 updated_location: Gainesville, Hall County
 address: 2157 Atlanta Highway, Gainesville, GA 30504
 latitude: 34.2525104
@@ -17882,6 +18144,7 @@
           <t>chunk_type: identity
 company: otr wheel engineering inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Rome, Floyd County</t>
         </is>
@@ -17959,6 +18222,7 @@
         <is>
           <t>chunk_type: location_employment
 company: otr wheel engineering inc.
+state: Georgia
 updated_location: Rome, Floyd County
 address: 6 Riverside Industrial Park, Rome, GA 30161
 latitude: 34.2805120276445
@@ -18015,6 +18279,7 @@
           <t>chunk_type: identity
 company: paccar
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Morrow, Clayton County</t>
         </is>
@@ -18092,6 +18357,7 @@
         <is>
           <t>chunk_type: location_employment
 company: paccar
+state: Georgia
 updated_location: Morrow, Clayton County
 address: 6853 Southlake Pkwy, Morrow, GA 30260
 latitude: 33.5675979753355
@@ -18148,6 +18414,7 @@
           <t>chunk_type: identity
 company: pai industries inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Mableton, Cobb County</t>
         </is>
@@ -18225,6 +18492,7 @@
         <is>
           <t>chunk_type: location_employment
 company: pai industries inc.
+state: Georgia
 updated_location: Mableton, Cobb County
 address: 2125 Clay Drive, Mableton, GA 30126
 latitude: 33.9234048
@@ -18281,6 +18549,7 @@
           <t>chunk_type: identity
 company: pak-lite inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Suwanee, Gwinnett County</t>
         </is>
@@ -18358,6 +18627,7 @@
         <is>
           <t>chunk_type: location_employment
 company: pak-lite inc.
+state: Georgia
 updated_location: Suwanee, Gwinnett County
 address: 550 Old Peachtree Rd NW, Suwanee, GA 30024
 latitude: 34.0114815633921
@@ -18414,6 +18684,7 @@
           <t>chunk_type: identity
 company: panasonic automotive systems co.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Peachtree City, Fayette County</t>
         </is>
@@ -18491,6 +18762,7 @@
         <is>
           <t>chunk_type: location_employment
 company: panasonic automotive systems co.
+state: Georgia
 updated_location: Peachtree City, Fayette County
 address: 1 Panasonic Way, Peachtree City, GA 30269
 latitude: 33.3586677099571
@@ -18547,6 +18819,7 @@
           <t>chunk_type: identity
 company: panasonic automotive systems co.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Peachtree City, Fayette County</t>
         </is>
@@ -18624,6 +18897,7 @@
         <is>
           <t>chunk_type: location_employment
 company: panasonic automotive systems co.
+state: Georgia
 updated_location: Peachtree City, Fayette County
 address: 1 Panasonic Way, Peachtree City, GA 30269
 latitude: 33.3540321602237
@@ -18680,6 +18954,7 @@
           <t>chunk_type: identity
 company: panduit corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Cumming, Forsyth County</t>
         </is>
@@ -18757,6 +19032,7 @@
         <is>
           <t>chunk_type: location_employment
 company: panduit corp.
+state: Georgia
 updated_location: Cumming, Forsyth County
 address: 1819 Atlanta Hwy, Cumming, GA 30040
 latitude: 34.1661720605728
@@ -18813,6 +19089,7 @@
           <t>chunk_type: identity
 company: peerless-winsmith inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Flowery Branch, Hall County</t>
         </is>
@@ -18890,6 +19167,7 @@
         <is>
           <t>chunk_type: location_employment
 company: peerless-winsmith inc.
+state: Georgia
 updated_location: Flowery Branch, Hall County
 address: 4510 Cantrell Road, Flowery Branch, GA 30542
 latitude: 34.1933557356756
@@ -18946,6 +19224,7 @@
           <t>chunk_type: identity
 company: perkins small engines llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Griffin, Spalding County</t>
         </is>
@@ -19023,6 +19302,7 @@
         <is>
           <t>chunk_type: location_employment
 company: perkins small engines llc
+state: Georgia
 updated_location: Griffin, Spalding County
 address: 325 Green Valley Road, Griffin, GA 30224
 latitude: 33.2313080586117
@@ -19079,6 +19359,7 @@
           <t>chunk_type: identity
 company: peterson spring
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Athens, Clarke County</t>
         </is>
@@ -19156,6 +19437,7 @@
         <is>
           <t>chunk_type: location_employment
 company: peterson spring
+state: Georgia
 updated_location: Athens, Clarke County
 address: 600 Old Hull Road, Athens, GA 30601
 latitude: 33.9865336091146
@@ -19212,6 +19494,7 @@
           <t>chunk_type: identity
 company: pha body systems llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Bloomingdale, Chatham County</t>
         </is>
@@ -19289,6 +19572,7 @@
         <is>
           <t>chunk_type: location_employment
 company: pha body systems llc
+state: Georgia
 updated_location: Bloomingdale, Chatham County
 address: 300 Monahan Drive, Bloomingdale, GA 31302
 latitude: 32.1009741405683
@@ -19345,6 +19629,7 @@
           <t>chunk_type: identity
 company: piedmont automotive products inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Clarkesville, Habersham County</t>
         </is>
@@ -19422,6 +19707,7 @@
         <is>
           <t>chunk_type: location_employment
 company: piedmont automotive products inc.
+state: Georgia
 updated_location: Clarkesville, Habersham County
 address: 1058 Rocky Branch Rd, Clarkesville, GA 30523
 latitude: 34.6078319
@@ -19478,6 +19764,7 @@
           <t>chunk_type: identity
 company: piolax corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Canton, Cherokee County</t>
         </is>
@@ -19555,6 +19842,7 @@
         <is>
           <t>chunk_type: location_employment
 company: piolax corp.
+state: Georgia
 updated_location: Canton, Cherokee County
 address: 139 Etowah Industrial Court, Canton, GA 30114
 latitude: 34.2456357508315
@@ -19611,6 +19899,7 @@
           <t>chunk_type: identity
 company: pirelli tire north america llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Albany, Dougherty County</t>
         </is>
@@ -19688,6 +19977,7 @@
         <is>
           <t>chunk_type: location_employment
 company: pirelli tire north america llc
+state: Georgia
 updated_location: Albany, Dougherty County
 address: 2819 Old Dawson Rd, Albany, GA 31707
 latitude: 31.6135962
@@ -19744,6 +20034,7 @@
           <t>chunk_type: identity
 company: porsche cars north america inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Atlanta, Fulton County</t>
         </is>
@@ -19821,6 +20112,7 @@
         <is>
           <t>chunk_type: location_employment
 company: porsche cars north america inc.
+state: Georgia
 updated_location: Atlanta, Fulton County
 address: 1 Porsche Dr, Atlanta, GA 30328
 latitude: 33.6520232116159
@@ -19877,6 +20169,7 @@
           <t>chunk_type: identity
 company: ppg industries inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Calhoun, Whitfield County</t>
         </is>
@@ -19954,6 +20247,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ppg industries inc.
+state: Georgia
 updated_location: Calhoun, Whitfield County
 address: 500 Enterprise Dr, Calhoun, GA 30701
 latitude: 34.6994514
@@ -20010,6 +20304,7 @@
           <t>chunk_type: identity
 company: propex operating co. llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Pooler, Chatham County</t>
         </is>
@@ -20087,6 +20382,7 @@
         <is>
           <t>chunk_type: location_employment
 company: propex operating co. llc
+state: Georgia
 updated_location: Pooler, Chatham County
 address: 490 Chatham Pkwy, Pooler, GA 31322
 latitude: 32.0941218
@@ -20143,6 +20439,7 @@
           <t>chunk_type: identity
 company: qsr inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: LaGrange, Clayton County</t>
         </is>
@@ -20220,6 +20517,7 @@
         <is>
           <t>chunk_type: location_employment
 company: qsr inc.
+state: Georgia
 updated_location: LaGrange, Clayton County
 address: 135 QSR Rd, LaGrange, GA 30240
 latitude: 33.555885
@@ -20276,6 +20574,7 @@
           <t>chunk_type: identity
 company: racemark international llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Gray, Jones County</t>
         </is>
@@ -20353,6 +20652,7 @@
         <is>
           <t>chunk_type: location_employment
 company: racemark international llc
+state: Georgia
 updated_location: Gray, Jones County
 address: 152 Racemark Dr, Gray, GA 31032
 latitude: 32.991607
@@ -20409,6 +20709,7 @@
           <t>chunk_type: identity
 company: realtruck
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Peachtree City, Chattooga County</t>
         </is>
@@ -20486,6 +20787,7 @@
         <is>
           <t>chunk_type: location_employment
 company: realtruck
+state: Georgia
 updated_location: Peachtree City, Chattooga County
 address: 1656 Airport Rd N, Peachtree City, GA 30269
 latitude: 34.588242
@@ -20542,6 +20844,7 @@
           <t>chunk_type: identity
 company: rivian automotive
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Atlanta, Fulton County</t>
         </is>
@@ -20619,6 +20922,7 @@
         <is>
           <t>chunk_type: location_employment
 company: rivian automotive
+state: Georgia
 updated_location: Atlanta, Fulton County
 address: 1090 Roberts Dr NW, Atlanta, GA 30318
 latitude: 33.720227
@@ -20675,6 +20979,7 @@
           <t>chunk_type: identity
 company: robert bosch llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Flowery Branch, Gwinnett County</t>
         </is>
@@ -20752,6 +21057,7 @@
         <is>
           <t>chunk_type: location_employment
 company: robert bosch llc
+state: Georgia
 updated_location: Flowery Branch, Gwinnett County
 address: 6330 W Broad St, Flowery Branch, GA 30542
 latitude: 34.1062368
@@ -20808,6 +21114,7 @@
           <t>chunk_type: identity
 company: saft america inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Cataula, Harris County</t>
         </is>
@@ -20885,6 +21192,7 @@
         <is>
           <t>chunk_type: location_employment
 company: saft america inc.
+state: Georgia
 updated_location: Cataula, Harris County
 address: 15621 Hopewell Church Rd, Cataula, GA 31804
 latitude: 32.8217618
@@ -20941,6 +21249,7 @@
           <t>chunk_type: identity
 company: sejong georgia llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Jefferson, Jackson County</t>
         </is>
@@ -21018,6 +21327,7 @@
         <is>
           <t>chunk_type: location_employment
 company: sejong georgia llc
+state: Georgia
 updated_location: Jefferson, Jackson County
 address: 100 Sejong Way, Jefferson, GA 30549
 latitude: 34.10601
@@ -21074,6 +21384,7 @@
           <t>chunk_type: identity
 company: seohan auto usa
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: LaGrange, Lamar County</t>
         </is>
@@ -21151,6 +21462,7 @@
         <is>
           <t>chunk_type: location_employment
 company: seohan auto usa
+state: Georgia
 updated_location: LaGrange, Lamar County
 address: 850 Lamar St, LaGrange, GA 30240
 latitude: 33.0528839
@@ -21207,6 +21519,7 @@
           <t>chunk_type: identity
 company: seoyon e-hwa
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: West Point, Troup County</t>
         </is>
@@ -21284,6 +21597,7 @@
         <is>
           <t>chunk_type: location_employment
 company: seoyon e-hwa
+state: Georgia
 updated_location: West Point, Troup County
 address: 200 Seoyon E-HWA Blvd, West Point, GA 31833
 latitude: 32.903183
@@ -21340,6 +21654,7 @@
           <t>chunk_type: identity
 company: seoyon e-hwa interior systems
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: West Point, Troup County</t>
         </is>
@@ -21417,6 +21732,7 @@
         <is>
           <t>chunk_type: location_employment
 company: seoyon e-hwa interior systems
+state: Georgia
 updated_location: West Point, Troup County
 address: 200 Seoyon E-HWA Blvd, West Point, GA 31833
 latitude: 32.8772531
@@ -21473,6 +21789,7 @@
           <t>chunk_type: identity
 company: sewon america inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: LaGrange, Troup County</t>
         </is>
@@ -21550,6 +21867,7 @@
         <is>
           <t>chunk_type: location_employment
 company: sewon america inc.
+state: Georgia
 updated_location: LaGrange, Troup County
 address: 210 Sewon Dr, LaGrange, GA 30241
 latitude: 33.0501
@@ -21606,6 +21924,7 @@
           <t>chunk_type: identity
 company: sewon america inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: LaGrange, Troup County</t>
         </is>
@@ -21683,6 +22002,7 @@
         <is>
           <t>chunk_type: location_employment
 company: sewon america inc.
+state: Georgia
 updated_location: LaGrange, Troup County
 address: 210 Sewon Dr, LaGrange, GA 30241
 latitude: 33.0501
@@ -21739,6 +22059,7 @@
           <t>chunk_type: identity
 company: sewon america inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: LaGrange, Troup County</t>
         </is>
@@ -21816,6 +22137,7 @@
         <is>
           <t>chunk_type: location_employment
 company: sewon america inc.
+state: Georgia
 updated_location: LaGrange, Troup County
 address: 210 Sewon Dr, LaGrange, GA 30241
 latitude: 33.0501
@@ -21872,6 +22194,7 @@
           <t>chunk_type: identity
 company: shiroki north america inc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: LaGrange, Clayton County</t>
         </is>
@@ -21949,6 +22272,7 @@
         <is>
           <t>chunk_type: location_employment
 company: shiroki north america inc
+state: Georgia
 updated_location: LaGrange, Clayton County
 address: 100 Shiroki Way, LaGrange, GA 30241
 latitude: 33.558724
@@ -22005,6 +22329,7 @@
           <t>chunk_type: identity
 company: sk battery america
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Ellabell, Bryan County</t>
         </is>
@@ -22082,6 +22407,7 @@
         <is>
           <t>chunk_type: location_employment
 company: sk battery america
+state: Georgia
 updated_location: Ellabell, Bryan County
 address: 700 Hyundai Blvd, Ellabell, GA 31308
 latitude: 32.159233
@@ -22138,6 +22464,7 @@
           <t>chunk_type: identity
 company: skf usa inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Ringgold, Catoosa County</t>
         </is>
@@ -22215,6 +22542,7 @@
         <is>
           <t>chunk_type: location_employment
 company: skf usa inc.
+state: Georgia
 updated_location: Ringgold, Catoosa County
 address: 301 David Fletcher Dr, Ringgold, GA 30736
 latitude: 34.907514
@@ -22271,6 +22599,7 @@
           <t>chunk_type: identity
 company: solvay specialty polymers usa llc
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Augusta, Elbert County</t>
         </is>
@@ -22348,6 +22677,7 @@
         <is>
           <t>chunk_type: location_employment
 company: solvay specialty polymers usa llc
+state: Georgia
 updated_location: Augusta, Elbert County
 address: 600 Patterson Ave, Augusta, GA 30901
 latitude: 34.1033951
@@ -22404,6 +22734,7 @@
           <t>chunk_type: identity
 company: southern switches corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Dahlonega, Lumpkin County</t>
         </is>
@@ -22481,6 +22812,7 @@
         <is>
           <t>chunk_type: location_employment
 company: southern switches corp.
+state: Georgia
 updated_location: Dahlonega, Lumpkin County
 address: 715 Happy Hollow Rd, Dahlonega, GA 30533
 latitude: 34.5298911539072
@@ -22537,6 +22869,7 @@
           <t>chunk_type: identity
 company: srg global inc.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Covington, Newton County</t>
         </is>
@@ -22614,6 +22947,7 @@
         <is>
           <t>chunk_type: location_employment
 company: srg global inc.
+state: Georgia
 updated_location: Covington, Newton County
 address: 10116 Industrial Blvd NE, Covington, GA 30014
 latitude: 33.6130210157665
@@ -22670,6 +23004,7 @@
           <t>chunk_type: identity
 company: stryten energy
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Alpharetta, Forsyth County</t>
         </is>
@@ -22747,6 +23082,7 @@
         <is>
           <t>chunk_type: location_employment
 company: stryten energy
+state: Georgia
 updated_location: Alpharetta, Forsyth County
 address: 5925 Cabot Pkwy, Alpharetta, GA 30005
 latitude: 34.1187111
@@ -22803,6 +23139,7 @@
           <t>chunk_type: identity
 company: suhner manufacturing corp.
 category: Tier 1
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Rome, Floyd County</t>
         </is>
@@ -22880,6 +23217,7 @@
         <is>
           <t>chunk_type: location_employment
 company: suhner manufacturing corp.
+state: Georgia
 updated_location: Rome, Floyd County
 address: 43 Anderson Rd SW, Rome, GA 30161
 latitude: 34.2085971300834
@@ -22936,6 +23274,7 @@
           <t>chunk_type: identity
 company: sungeel recycling park georgia
 category: Tier 2/3
+state: Georgia
 industry_group: Miscellaneous Manufacturing Industries
 updated_location: Duluth, Gwinnett County</t>
         </is>
@@ -23013,6 +23352,7 @@
         <is>
           <t>chunk_type: location_employment
 company: sungeel recycling park georgia
+state: Georgia
 updated_location: Duluth, Gwinnett County
 address: 3237 Satellite Blvd, Suite 175, Duluth, GA 30096
 latitude: 33.962713
@@ -23069,6 +23409,7 @@
           <t>chunk_type: identity
 company: superior essex inc.
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Kennesaw, Cobb County</t>
         </is>
@@ -23146,6 +23487,7 @@
         <is>
           <t>chunk_type: location_employment
 company: superior essex inc.
+state: Georgia
 updated_location: Kennesaw, Cobb County
 address: 3600 Cobb International Blvd NW, Kennesaw, GA 30152
 latitude: 33.9990198954442
@@ -23202,6 +23544,7 @@
           <t>chunk_type: identity
 company: suzuki manufacturing of america corp.
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Rome, Douglas County</t>
         </is>
@@ -23279,6 +23622,7 @@
         <is>
           <t>chunk_type: location_employment
 company: suzuki manufacturing of america corp.
+state: Georgia
 updated_location: Rome, Douglas County
 address: 1000 McIntosh Trail SW, Rome, GA 30165
 latitude: 33.771861
@@ -23335,6 +23679,7 @@
           <t>chunk_type: identity
 company: tci powder coatings
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Ellaville, Schley County</t>
         </is>
@@ -23412,6 +23757,7 @@
         <is>
           <t>chunk_type: location_employment
 company: tci powder coatings
+state: Georgia
 updated_location: Ellaville, Schley County
 address: 610 Dixon Dr, Ellaville, GA 31806
 latitude: 32.2336427
@@ -23468,6 +23814,7 @@
           <t>chunk_type: identity
 company: tdk components usa inc.
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Silver Creek, Floyd County</t>
         </is>
@@ -23545,6 +23892,7 @@
         <is>
           <t>chunk_type: location_employment
 company: tdk components usa inc.
+state: Georgia
 updated_location: Silver Creek, Floyd County
 address: 4058 Rockmart Rd, Silver Creek, GA 30173
 latitude: 34.1773552
@@ -23601,6 +23949,7 @@
           <t>chunk_type: identity
 company: te connectivity
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Kennesaw, Cobb County</t>
         </is>
@@ -23678,6 +24027,7 @@
         <is>
           <t>chunk_type: location_employment
 company: te connectivity
+state: Georgia
 updated_location: Kennesaw, Cobb County
 address: 3295 Cobb International Blvd NW, Kennesaw, GA 30152
 latitude: 34.0027115
@@ -23734,6 +24084,7 @@
           <t>chunk_type: identity
 company: teklas usa
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Calhoun, Gordon County</t>
         </is>
@@ -23811,6 +24162,7 @@
         <is>
           <t>chunk_type: location_employment
 company: teklas usa
+state: Georgia
 updated_location: Calhoun, Gordon County
 address: 320 S Industrial Blvd, Calhoun, GA 30701
 latitude: 34.4762350916405
@@ -23867,6 +24219,7 @@
           <t>chunk_type: identity
 company: textron specialized vehicles
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Augusta, Richmond County</t>
         </is>
@@ -23944,6 +24297,7 @@
         <is>
           <t>chunk_type: location_employment
 company: textron specialized vehicles
+state: Georgia
 updated_location: Augusta, Richmond County
 address: 1451 Marvin Griffin Rd, Augusta, GA 30906
 latitude: 33.3956126
@@ -24000,6 +24354,7 @@
           <t>chunk_type: identity
 company: thermal ceramics inc.
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Augusta, Richmond County</t>
         </is>
@@ -24077,6 +24432,7 @@
         <is>
           <t>chunk_type: location_employment
 company: thermal ceramics inc.
+state: Georgia
 updated_location: Augusta, Richmond County
 address: 2190 N Leg Rd, Augusta, GA 30909
 latitude: 33.4565319
@@ -24133,6 +24489,7 @@
           <t>chunk_type: identity
 company: thomson plastics inc.
 category: OEM
+state: Georgia
 industry_group: Transportation Equipment
 updated_location: Monroe, Walton County</t>
         </is>
@@ -24210,6 +24567,7 @@
         <is>
           <t>chunk_type: location_employment
 company: thomson plastics inc.
+state: Georgia
 updated_location: Monroe, Walton County
 address: 1440 H D Atha Rd, Monroe, GA 30656
 latitude: 33.774282
@@ -24266,6 +24624,7 @@
           <t>chunk_type: identity
 company: ti fluid systems
 category: OEM Footprint
+state: Georgia
 industry_group: Passenger vehicles (EV + ICE)
 updated_location: Cartersville, Bartow County</t>
         </is>
@@ -24343,6 +24702,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ti fluid systems
+state: Georgia
 updated_location: Cartersville, Bartow County
 address: 2 Swisher Dr, Cartersville, GA 30120
 latitude: 34.1446878814573
@@ -24399,6 +24759,7 @@
           <t>chunk_type: identity
 company: ti fluid systems
 category: OEM
+state: Georgia
 industry_group: Automotive safety systems and restraints
 updated_location: Cartersville, Bartow County</t>
         </is>
@@ -24476,6 +24837,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ti fluid systems
+state: Georgia
 updated_location: Cartersville, Bartow County
 address: 2 Swisher Dr, Cartersville, GA 30120
 latitude: 34.1446878814573
@@ -24532,6 +24894,7 @@
           <t>chunk_type: identity
 company: tie down engineering
 category: OEM Footprint
+state: Georgia
 industry_group: Heavy-duty trucks
 updated_location: Atlanta, Fulton County</t>
         </is>
@@ -24609,6 +24972,7 @@
         <is>
           <t>chunk_type: location_employment
 company: tie down engineering
+state: Georgia
 updated_location: Atlanta, Fulton County
 address: 605 Stonehill Dr SW, Atlanta, GA 30336
 latitude: 33.7398598923206
@@ -24665,6 +25029,7 @@
           <t>chunk_type: identity
 company: tn americas holding inc.
 category: OEM Footprint
+state: Georgia
 industry_group: Commercial vehicles and powertrains
 updated_location: Cumming, Forsyth County</t>
         </is>
@@ -24742,6 +25107,7 @@
         <is>
           <t>chunk_type: location_employment
 company: tn americas holding inc.
+state: Georgia
 updated_location: Cumming, Forsyth County
 address: 2200 Pendley Rd, Cumming, GA 30041
 latitude: 34.1622969342683
@@ -24798,6 +25164,7 @@
           <t>chunk_type: identity
 company: toyota industries group (tacg-tica)
 category: OEM Footprint
+state: Georgia
 industry_group: Commercial vehicles and powertrains
 updated_location: Pendergrass, Jackson County</t>
         </is>
@@ -24875,6 +25242,7 @@
         <is>
           <t>chunk_type: location_employment
 company: toyota industries group (tacg-tica)
+state: Georgia
 updated_location: Pendergrass, Jackson County
 address: 1000 Valentine Industrial Pkwy, Pendergrass, GA 30567
 latitude: 34.1799504745923
@@ -24931,6 +25299,7 @@
           <t>chunk_type: identity
 company: trenton pressing
 category: OEM Footprint
+state: Georgia
 industry_group: Commercial vehicles (Kenworth, Peterbilt)
 updated_location: Trenton, Dade County</t>
         </is>
@@ -25008,6 +25377,7 @@
         <is>
           <t>chunk_type: location_employment
 company: trenton pressing
+state: Georgia
 updated_location: Trenton, Dade County
 address: 505 N Industrial Blvd, Trenton, GA 30752
 latitude: 34.8787288016289
@@ -25064,6 +25434,7 @@
           <t>chunk_type: identity
 company: trenton pressing inc.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive precision components
 updated_location: Trenton, Dade County</t>
         </is>
@@ -25141,6 +25512,7 @@
         <is>
           <t>chunk_type: location_employment
 company: trenton pressing inc.
+state: Georgia
 updated_location: Trenton, Dade County
 address: 505 N Industrial Blvd, Trenton, GA 30752
 latitude: 34.8787288016289
@@ -25197,6 +25569,7 @@
           <t>chunk_type: identity
 company: valeo
 category: OEM Supply Chain
+state: Unknown
 industry_group: Automotive parts manufacturing
 updated_location: Unknown</t>
         </is>
@@ -25274,6 +25647,7 @@
         <is>
           <t>chunk_type: location_employment
 company: valeo
+state: Unknown
 updated_location: Unknown
 address: Unknown
 latitude: Unknown
@@ -25330,6 +25704,7 @@
           <t>chunk_type: identity
 company: vanguard national trailer corp.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive structural components
 updated_location: Trenton, Dade County</t>
         </is>
@@ -25407,6 +25782,7 @@
         <is>
           <t>chunk_type: location_employment
 company: vanguard national trailer corp.
+state: Georgia
 updated_location: Trenton, Dade County
 address: 8 Vanguard Dr, Trenton, GA 30752
 latitude: 34.886297855747
@@ -25463,6 +25839,7 @@
           <t>chunk_type: identity
 company: vernay
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive stamping and assemblies
 updated_location: Griffin, Spalding County</t>
         </is>
@@ -25540,6 +25917,7 @@
         <is>
           <t>chunk_type: location_employment
 company: vernay
+state: Georgia
 updated_location: Griffin, Spalding County
 address: 804 Greenbelt Pkwy, Griffin, GA 30223
 latitude: 33.2377968959845
@@ -25596,6 +25974,7 @@
           <t>chunk_type: identity
 company: vista metals corp.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive modules and components
 updated_location: Adairsville, Bartow County</t>
         </is>
@@ -25673,6 +26052,7 @@
         <is>
           <t>chunk_type: location_employment
 company: vista metals corp.
+state: Georgia
 updated_location: Adairsville, Bartow County
 address: 800 Martin Luther King Jr Dr, Adairsville, GA 30103
 latitude: 34.3676324336592
@@ -25729,6 +26109,7 @@
           <t>chunk_type: identity
 company: voestalpine automotive body parts inc.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive components
 updated_location: Cartersville, Bartow County</t>
         </is>
@@ -25806,6 +26187,7 @@
         <is>
           <t>chunk_type: location_employment
 company: voestalpine automotive body parts inc.
+state: Georgia
 updated_location: Cartersville, Bartow County
 address: 4334 Highway 20 SE, Cartersville, GA 30121
 latitude: 34.181471
@@ -25862,6 +26244,7 @@
           <t>chunk_type: identity
 company: volvo cars usa
 category: OEM Supply Chain
+state: New Jersey
 industry_group: Automotive plastics
 updated_location: Rabun County</t>
         </is>
@@ -25939,6 +26322,7 @@
         <is>
           <t>chunk_type: location_employment
 company: volvo cars usa
+state: New Jersey
 updated_location: Rabun County
 address: 1800 Volvo Place, Mahwah, NJ 07430
 latitude: 41.0740427635951
@@ -25995,6 +26379,7 @@
           <t>chunk_type: identity
 company: volvo group north america
 category: OEM Supply Chain
+state: North Carolina
 industry_group: Metal stamping and assemblies
 updated_location: Lincoln County</t>
         </is>
@@ -26072,6 +26457,7 @@
         <is>
           <t>chunk_type: location_employment
 company: volvo group north america
+state: North Carolina
 updated_location: Lincoln County
 address: 7900 National Service Rd, Greensboro, NC 27409
 latitude: 36.0818642621738
@@ -26128,6 +26514,7 @@
           <t>chunk_type: identity
 company: wabash national corp.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive plastic components
 updated_location: Ellenwood, Clayton County</t>
         </is>
@@ -26205,6 +26592,7 @@
         <is>
           <t>chunk_type: location_employment
 company: wabash national corp.
+state: Georgia
 updated_location: Ellenwood, Clayton County
 address: 2620 Campbell Blvd, Ellenwood, GA 30294
 latitude: 33.6209605672664
@@ -26261,6 +26649,7 @@
           <t>chunk_type: identity
 company: wheelabrator group inc.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive textiles and interiors
 updated_location: LaGrange, Troup County</t>
         </is>
@@ -26338,6 +26727,7 @@
         <is>
           <t>chunk_type: location_employment
 company: wheelabrator group inc.
+state: Georgia
 updated_location: LaGrange, Troup County
 address: 1606 Executive Dr, LaGrange, GA 30240
 latitude: 33.0087223514155
@@ -26394,6 +26784,7 @@
           <t>chunk_type: identity
 company: wika usa
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive wiring systems
 updated_location: Lawrenceville, Gwinnett County</t>
         </is>
@@ -26471,6 +26862,7 @@
         <is>
           <t>chunk_type: location_employment
 company: wika usa
+state: Georgia
 updated_location: Lawrenceville, Gwinnett County
 address: 1000 Wiegand Blvd, Lawrenceville, GA 30043
 latitude: 33.960968631134
@@ -26527,6 +26919,7 @@
           <t>chunk_type: identity
 company: woodbridge foam corp.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive electrical systems
 updated_location: Lithonia, DeKalb County</t>
         </is>
@@ -26604,6 +26997,7 @@
         <is>
           <t>chunk_type: location_employment
 company: woodbridge foam corp.
+state: Georgia
 updated_location: Lithonia, DeKalb County
 address: 2399 S Stone Mountain Lithonia Rd, Lithonia, GA 30058
 latitude: 33.737555
@@ -26660,6 +27054,7 @@
           <t>chunk_type: identity
 company: woory industrial co.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Electrical connectors and sensors
 updated_location: Dublin, Laurens County</t>
         </is>
@@ -26737,6 +27132,7 @@
         <is>
           <t>chunk_type: location_employment
 company: woory industrial co.
+state: Georgia
 updated_location: Dublin, Laurens County
 address: 404 Kellam Rd, Dublin, GA 31021
 latitude: 32.5286348559853
@@ -26793,6 +27189,7 @@
           <t>chunk_type: identity
 company: yachiyo manufacturing of america llc
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive seating and E‑systems
 updated_location: Carrollton, Carroll County</t>
         </is>
@@ -26870,6 +27267,7 @@
         <is>
           <t>chunk_type: location_employment
 company: yachiyo manufacturing of america llc
+state: Georgia
 updated_location: Carrollton, Carroll County
 address: 565 Beulah Church Rd, Carrollton, GA 30117
 latitude: 33.601430192463
@@ -26926,6 +27324,7 @@
           <t>chunk_type: identity
 company: yamaha motor manufacturing corp.
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive electronics
 updated_location: Newnan, Coweta County</t>
         </is>
@@ -27003,6 +27402,7 @@
         <is>
           <t>chunk_type: location_employment
 company: yamaha motor manufacturing corp.
+state: Georgia
 updated_location: Newnan, Coweta County
 address: 1000 Georgia Highway 34E, Newnan, GA
 latitude: 33.4024771
@@ -27059,6 +27459,7 @@
           <t>chunk_type: identity
 company: yazaki north america
 category: OEM Footprint
+state: Georgia
 industry_group: Automotive electronics and systems
 updated_location: Spalding County</t>
         </is>
@@ -27136,6 +27537,7 @@
         <is>
           <t>chunk_type: location_employment
 company: yazaki north america
+state: Georgia
 updated_location: Spalding County
 address: 375 Airport Rd, Griffin, Georgia
 latitude: 33.2266019
@@ -27192,6 +27594,7 @@
           <t>chunk_type: identity
 company: ykk usa inc.
 category: OEM Footprint
+state: Georgia
 industry_group: Automotive electronics and safety systems
 updated_location: Marietta, Cobb County</t>
         </is>
@@ -27269,6 +27672,7 @@
         <is>
           <t>chunk_type: location_employment
 company: ykk usa inc.
+state: Georgia
 updated_location: Marietta, Cobb County
 address: 1300 Cobb Industrial Dr, Marietta, GA 30066
 latitude: 33.9790253535143
@@ -27325,6 +27729,7 @@
           <t>chunk_type: identity
 company: zf gainesville llc
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive systems and components
 updated_location: Gainesville, Hall County</t>
         </is>
@@ -27402,6 +27807,7 @@
         <is>
           <t>chunk_type: location_employment
 company: zf gainesville llc
+state: Georgia
 updated_location: Gainesville, Hall County
 address: 1261 Palmour Dr SW, Gainesville, GA 30501
 latitude: 34.2647050791808
@@ -27458,6 +27864,7 @@
           <t>chunk_type: identity
 company: zf gainesville llc
 category: OEM Supply Chain
+state: Georgia
 industry_group: Automotive thermal and electronics systems
 updated_location: Gainesville, Hall County</t>
         </is>
@@ -27535,6 +27942,7 @@
         <is>
           <t>chunk_type: location_employment
 company: zf gainesville llc
+state: Georgia
 updated_location: Gainesville, Hall County
 address: 1261 Palmour Dr SW, Gainesville, GA 30501
 latitude: 34.2647050791808
@@ -27591,6 +27999,7 @@
           <t>chunk_type: identity
 company: zf gainesville llc
 category: OEM Footprint
+state: Georgia
 industry_group: Automotive powertrain and thermal systems
 updated_location: Gainesville, Hall County</t>
         </is>
@@ -27668,6 +28077,7 @@
         <is>
           <t>chunk_type: location_employment
 company: zf gainesville llc
+state: Georgia
 updated_location: Gainesville, Hall County
 address: Unknown
 latitude: Unknown
